--- a/artfynd/A 32029-2023 artfynd.xlsx
+++ b/artfynd/A 32029-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122593750</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32029-2023 artfynd.xlsx
+++ b/artfynd/A 32029-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,382 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122881442</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57394</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vinarheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>514215</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6661518</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Lif</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Lif</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122881441</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57128</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gråtrut</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Larus argentatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pontoppidan, 1763</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vinarheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>514215</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6661518</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Lif</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Lif</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122881440</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56529</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vinarheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>514215</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6661518</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Lif</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Lif</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32029-2023 artfynd.xlsx
+++ b/artfynd/A 32029-2023 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122881441</v>
+        <v>122881440</v>
       </c>
       <c r="B4" t="n">
-        <v>57128</v>
+        <v>56529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,37 +939,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102966</v>
+        <v>100045</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122881440</v>
+        <v>122881441</v>
       </c>
       <c r="B5" t="n">
-        <v>56529</v>
+        <v>57128</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,37 +1063,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100045</v>
+        <v>102966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 32029-2023 artfynd.xlsx
+++ b/artfynd/A 32029-2023 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122881442</v>
+        <v>122881441</v>
       </c>
       <c r="B3" t="n">
-        <v>57394</v>
+        <v>57128</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,25 +811,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>102966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,15 +837,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -927,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122881440</v>
+        <v>122881442</v>
       </c>
       <c r="B4" t="n">
-        <v>56529</v>
+        <v>57394</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,20 +935,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100045</v>
+        <v>100067</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -962,14 +958,18 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122881441</v>
+        <v>122881440</v>
       </c>
       <c r="B5" t="n">
-        <v>57128</v>
+        <v>56529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,37 +1063,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102966</v>
+        <v>100045</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 32029-2023 artfynd.xlsx
+++ b/artfynd/A 32029-2023 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122881441</v>
+        <v>122881440</v>
       </c>
       <c r="B3" t="n">
-        <v>57128</v>
+        <v>56529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,37 +811,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102966</v>
+        <v>100045</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122881442</v>
+        <v>122881441</v>
       </c>
       <c r="B4" t="n">
-        <v>57394</v>
+        <v>57128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,25 +935,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>102966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,15 +961,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1051,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122881440</v>
+        <v>122881442</v>
       </c>
       <c r="B5" t="n">
-        <v>56529</v>
+        <v>57394</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,20 +1059,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100045</v>
+        <v>100067</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1086,14 +1082,18 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 32029-2023 artfynd.xlsx
+++ b/artfynd/A 32029-2023 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122881440</v>
+        <v>122881442</v>
       </c>
       <c r="B3" t="n">
-        <v>56529</v>
+        <v>57394</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100045</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,14 +834,18 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -1047,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122881442</v>
+        <v>122881440</v>
       </c>
       <c r="B5" t="n">
-        <v>57394</v>
+        <v>56529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,20 +1063,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100067</v>
+        <v>100045</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,18 +1086,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 32029-2023 artfynd.xlsx
+++ b/artfynd/A 32029-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>122881442</v>
       </c>
       <c r="B3" t="n">
-        <v>57394</v>
+        <v>57397</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122881440</v>
+        <v>122881441</v>
       </c>
       <c r="B4" t="n">
-        <v>56529</v>
+        <v>57131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,37 +939,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100045</v>
+        <v>102966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122881441</v>
+        <v>122881440</v>
       </c>
       <c r="B5" t="n">
-        <v>57128</v>
+        <v>56532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,37 +1063,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102966</v>
+        <v>100045</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 32029-2023 artfynd.xlsx
+++ b/artfynd/A 32029-2023 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122881442</v>
+        <v>122881441</v>
       </c>
       <c r="B3" t="n">
-        <v>57397</v>
+        <v>57131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,25 +811,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>102966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,15 +837,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -927,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122881441</v>
+        <v>122881442</v>
       </c>
       <c r="B4" t="n">
-        <v>57131</v>
+        <v>57397</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,25 +935,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102966</v>
+        <v>100067</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -965,11 +961,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>

--- a/artfynd/A 32029-2023 artfynd.xlsx
+++ b/artfynd/A 32029-2023 artfynd.xlsx
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122881442</v>
+        <v>122881440</v>
       </c>
       <c r="B4" t="n">
-        <v>57397</v>
+        <v>56532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,20 +935,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>100045</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,18 +958,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1051,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122881440</v>
+        <v>122881442</v>
       </c>
       <c r="B5" t="n">
-        <v>56532</v>
+        <v>57397</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,20 +1059,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100045</v>
+        <v>100067</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1086,14 +1082,18 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
